--- a/Shiny/Datos limpios/pricing_diario_total_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_total_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -6897,10 +6897,10 @@
         <v>5645.639999999999</v>
       </c>
       <c r="G251">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="H251">
-        <v>410059.26</v>
+        <v>409918.58</v>
       </c>
     </row>
     <row r="252">
@@ -7105,10 +7105,10 @@
         <v>3401.69</v>
       </c>
       <c r="G259">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="H259">
-        <v>438744.4300000001</v>
+        <v>438710.51</v>
       </c>
     </row>
     <row r="260">
@@ -7229,7 +7229,7 @@
         <v>72983.32000000001</v>
       </c>
       <c r="E264">
-        <v>481877.8100000001</v>
+        <v>480607.55</v>
       </c>
       <c r="F264">
         <v>3468.49</v>
@@ -7238,7 +7238,7 @@
         <v>100670.96</v>
       </c>
       <c r="H264">
-        <v>665943.84</v>
+        <v>664673.58</v>
       </c>
     </row>
     <row r="265">
@@ -7261,10 +7261,10 @@
         <v>563.99</v>
       </c>
       <c r="G265">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="H265">
-        <v>1706993.91</v>
+        <v>1706806.18</v>
       </c>
     </row>
     <row r="266">
@@ -7281,16 +7281,16 @@
         <v>206389.3</v>
       </c>
       <c r="E266">
-        <v>1574424.4</v>
+        <v>1574405.94</v>
       </c>
       <c r="F266">
         <v>1872.14</v>
       </c>
       <c r="G266">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="H266">
-        <v>2042044.69</v>
+        <v>2041026.23</v>
       </c>
     </row>
     <row r="267">
@@ -7307,7 +7307,7 @@
         <v>152926.75</v>
       </c>
       <c r="E267">
-        <v>837417.1100000001</v>
+        <v>837359.4</v>
       </c>
       <c r="F267">
         <v>5454.65</v>
@@ -7316,7 +7316,7 @@
         <v>106359.36</v>
       </c>
       <c r="H267">
-        <v>1144108.5</v>
+        <v>1144050.79</v>
       </c>
     </row>
     <row r="268">
@@ -7463,16 +7463,16 @@
         <v>70085.70999999999</v>
       </c>
       <c r="E273">
-        <v>380373.22</v>
+        <v>380369.38</v>
       </c>
       <c r="F273">
         <v>11864.14</v>
       </c>
       <c r="G273">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="H273">
-        <v>556041.9</v>
+        <v>555916.5700000001</v>
       </c>
     </row>
     <row r="274">
@@ -7489,7 +7489,7 @@
         <v>92329.42</v>
       </c>
       <c r="E274">
-        <v>370912.65</v>
+        <v>370765.3</v>
       </c>
       <c r="F274">
         <v>1132.62</v>
@@ -7498,7 +7498,7 @@
         <v>69660.97</v>
       </c>
       <c r="H274">
-        <v>557229.26</v>
+        <v>557081.91</v>
       </c>
     </row>
     <row r="275">
@@ -7515,16 +7515,16 @@
         <v>90230.02000000002</v>
       </c>
       <c r="E275">
-        <v>423023.69</v>
+        <v>423024.43</v>
       </c>
       <c r="F275">
         <v>12823.31</v>
       </c>
       <c r="G275">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="H275">
-        <v>660036.8800000001</v>
+        <v>659747.53</v>
       </c>
     </row>
     <row r="276">
@@ -7593,7 +7593,7 @@
         <v>97668.79000000001</v>
       </c>
       <c r="E278">
-        <v>227120.04</v>
+        <v>227000.04</v>
       </c>
       <c r="F278">
         <v>1361.07</v>
@@ -7602,7 +7602,7 @@
         <v>83410.52</v>
       </c>
       <c r="H278">
-        <v>427881.6800000001</v>
+        <v>427761.6800000001</v>
       </c>
     </row>
     <row r="279">
@@ -7625,10 +7625,10 @@
         <v>994.22</v>
       </c>
       <c r="G279">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="H279">
-        <v>420817.7</v>
+        <v>420662.43</v>
       </c>
     </row>
     <row r="280">
@@ -7781,10 +7781,10 @@
         <v>901.3099999999999</v>
       </c>
       <c r="G285">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="H285">
-        <v>324046.59</v>
+        <v>323750.03</v>
       </c>
     </row>
     <row r="286">
@@ -7882,13 +7882,13 @@
         <v>106043.07</v>
       </c>
       <c r="F289">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="G289">
         <v>107090.62</v>
       </c>
       <c r="H289">
-        <v>408688.26</v>
+        <v>407688.26</v>
       </c>
     </row>
     <row r="290">
@@ -8104,25 +8104,675 @@
         <v>45957</v>
       </c>
       <c r="B298">
-        <v>7950</v>
+        <v>19388.34</v>
       </c>
       <c r="C298">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="D298">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="E298">
-        <v>2677.84</v>
+        <v>56853.16</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>1289.08</v>
       </c>
       <c r="G298">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="H298">
-        <v>14047.84</v>
+        <v>211136.45</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B299">
+        <v>18221.26</v>
+      </c>
+      <c r="C299">
+        <v>11008.73</v>
+      </c>
+      <c r="D299">
+        <v>117118.26</v>
+      </c>
+      <c r="E299">
+        <v>118743.84</v>
+      </c>
+      <c r="F299">
+        <v>1556.12</v>
+      </c>
+      <c r="G299">
+        <v>102356.76</v>
+      </c>
+      <c r="H299">
+        <v>369004.97</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B300">
+        <v>11773</v>
+      </c>
+      <c r="C300">
+        <v>10770.94</v>
+      </c>
+      <c r="D300">
+        <v>95470.38</v>
+      </c>
+      <c r="E300">
+        <v>58551.82</v>
+      </c>
+      <c r="F300">
+        <v>1664.4</v>
+      </c>
+      <c r="G300">
+        <v>62442.2</v>
+      </c>
+      <c r="H300">
+        <v>240672.74</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B301">
+        <v>21536.23</v>
+      </c>
+      <c r="C301">
+        <v>11518.56</v>
+      </c>
+      <c r="D301">
+        <v>130203.01</v>
+      </c>
+      <c r="E301">
+        <v>55796.11</v>
+      </c>
+      <c r="F301">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="G301">
+        <v>92197.7</v>
+      </c>
+      <c r="H301">
+        <v>312143.67</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B302">
+        <v>31360</v>
+      </c>
+      <c r="C302">
+        <v>8032.99</v>
+      </c>
+      <c r="D302">
+        <v>146743.22</v>
+      </c>
+      <c r="E302">
+        <v>48408.11</v>
+      </c>
+      <c r="F302">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="G302">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="H302">
+        <v>332766.88</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>159.87</v>
+      </c>
+      <c r="E303">
+        <v>2215.14</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>1597.81</v>
+      </c>
+      <c r="H303">
+        <v>3972.82</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>13081.43</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>13081.43</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B305">
+        <v>26455.8</v>
+      </c>
+      <c r="C305">
+        <v>8996.65</v>
+      </c>
+      <c r="D305">
+        <v>137256.09</v>
+      </c>
+      <c r="E305">
+        <v>81738.89999999999</v>
+      </c>
+      <c r="F305">
+        <v>2699.28</v>
+      </c>
+      <c r="G305">
+        <v>99453.11</v>
+      </c>
+      <c r="H305">
+        <v>356599.83</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B306">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="C306">
+        <v>31218.63</v>
+      </c>
+      <c r="D306">
+        <v>100755.44</v>
+      </c>
+      <c r="E306">
+        <v>107688.57</v>
+      </c>
+      <c r="F306">
+        <v>1710.15</v>
+      </c>
+      <c r="G306">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="H306">
+        <v>360333.8700000001</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B307">
+        <v>20673.65</v>
+      </c>
+      <c r="C307">
+        <v>22130.88</v>
+      </c>
+      <c r="D307">
+        <v>295755.66</v>
+      </c>
+      <c r="E307">
+        <v>42870.54</v>
+      </c>
+      <c r="F307">
+        <v>4628.26</v>
+      </c>
+      <c r="G307">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="H307">
+        <v>481351.6900000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B308">
+        <v>12292.76</v>
+      </c>
+      <c r="C308">
+        <v>-5764.84</v>
+      </c>
+      <c r="D308">
+        <v>212826.47</v>
+      </c>
+      <c r="E308">
+        <v>111236.27</v>
+      </c>
+      <c r="F308">
+        <v>1946.28</v>
+      </c>
+      <c r="G308">
+        <v>71152.63</v>
+      </c>
+      <c r="H308">
+        <v>403689.57</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B309">
+        <v>23785.06</v>
+      </c>
+      <c r="C309">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="D309">
+        <v>127060.58</v>
+      </c>
+      <c r="E309">
+        <v>127863.62</v>
+      </c>
+      <c r="F309">
+        <v>2209.08</v>
+      </c>
+      <c r="G309">
+        <v>61774.31</v>
+      </c>
+      <c r="H309">
+        <v>352006.43</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>15</v>
+      </c>
+      <c r="D310">
+        <v>516.72</v>
+      </c>
+      <c r="E310">
+        <v>1378.62</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>254.2</v>
+      </c>
+      <c r="H310">
+        <v>2164.54</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>35</v>
+      </c>
+      <c r="E311">
+        <v>500</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="H311">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B312">
+        <v>14799.99</v>
+      </c>
+      <c r="C312">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="D312">
+        <v>147347.01</v>
+      </c>
+      <c r="E312">
+        <v>51602.62</v>
+      </c>
+      <c r="F312">
+        <v>2021.14</v>
+      </c>
+      <c r="G312">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="H312">
+        <v>316742.97</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B313">
+        <v>22060.6</v>
+      </c>
+      <c r="C313">
+        <v>15913.23</v>
+      </c>
+      <c r="D313">
+        <v>187223.45</v>
+      </c>
+      <c r="E313">
+        <v>68845.47</v>
+      </c>
+      <c r="F313">
+        <v>1437.55</v>
+      </c>
+      <c r="G313">
+        <v>92712.08</v>
+      </c>
+      <c r="H313">
+        <v>388192.38</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B314">
+        <v>10481.56</v>
+      </c>
+      <c r="C314">
+        <v>11562.86</v>
+      </c>
+      <c r="D314">
+        <v>122982.8</v>
+      </c>
+      <c r="E314">
+        <v>85335.42000000001</v>
+      </c>
+      <c r="F314">
+        <v>1078.46</v>
+      </c>
+      <c r="G314">
+        <v>109947.54</v>
+      </c>
+      <c r="H314">
+        <v>341388.64</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B315">
+        <v>15739.25</v>
+      </c>
+      <c r="C315">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="D315">
+        <v>195224.96</v>
+      </c>
+      <c r="E315">
+        <v>75975.76999999999</v>
+      </c>
+      <c r="F315">
+        <v>1881.48</v>
+      </c>
+      <c r="G315">
+        <v>145746.27</v>
+      </c>
+      <c r="H315">
+        <v>444560.96</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B316">
+        <v>14622.57</v>
+      </c>
+      <c r="C316">
+        <v>10007.08</v>
+      </c>
+      <c r="D316">
+        <v>359640.37</v>
+      </c>
+      <c r="E316">
+        <v>51099.35</v>
+      </c>
+      <c r="F316">
+        <v>1177.15</v>
+      </c>
+      <c r="G316">
+        <v>159314.17</v>
+      </c>
+      <c r="H316">
+        <v>595860.6900000001</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>1776.47</v>
+      </c>
+      <c r="E317">
+        <v>180</v>
+      </c>
+      <c r="F317">
+        <v>145</v>
+      </c>
+      <c r="G317">
+        <v>720</v>
+      </c>
+      <c r="H317">
+        <v>2821.47</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>800.28</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>500</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="H318">
+        <v>1300.28</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B319">
+        <v>31748.74</v>
+      </c>
+      <c r="C319">
+        <v>8849.66</v>
+      </c>
+      <c r="D319">
+        <v>113945.08</v>
+      </c>
+      <c r="E319">
+        <v>74008.22</v>
+      </c>
+      <c r="F319">
+        <v>743.95</v>
+      </c>
+      <c r="G319">
+        <v>113416.33</v>
+      </c>
+      <c r="H319">
+        <v>342711.98</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B320">
+        <v>27423.37</v>
+      </c>
+      <c r="C320">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="D320">
+        <v>80879.83</v>
+      </c>
+      <c r="E320">
+        <v>102518.02</v>
+      </c>
+      <c r="F320">
+        <v>480</v>
+      </c>
+      <c r="G320">
+        <v>116519.79</v>
+      </c>
+      <c r="H320">
+        <v>334487.11</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B321">
+        <v>27056</v>
+      </c>
+      <c r="C321">
+        <v>15932.94</v>
+      </c>
+      <c r="D321">
+        <v>113818.39</v>
+      </c>
+      <c r="E321">
+        <v>97366.82999999999</v>
+      </c>
+      <c r="F321">
+        <v>462.46</v>
+      </c>
+      <c r="G321">
+        <v>136266.54</v>
+      </c>
+      <c r="H321">
+        <v>390903.16</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B322">
+        <v>29415.74</v>
+      </c>
+      <c r="C322">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="D322">
+        <v>68768.36</v>
+      </c>
+      <c r="E322">
+        <v>66451.56</v>
+      </c>
+      <c r="F322">
+        <v>2027.73</v>
+      </c>
+      <c r="G322">
+        <v>100749.12</v>
+      </c>
+      <c r="H322">
+        <v>277102.79</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B323">
+        <v>10210</v>
+      </c>
+      <c r="C323">
+        <v>2256.3</v>
+      </c>
+      <c r="D323">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="E323">
+        <v>11084.31</v>
+      </c>
+      <c r="F323">
+        <v>0</v>
+      </c>
+      <c r="G323">
+        <v>20391.37</v>
+      </c>
+      <c r="H323">
+        <v>50991.29</v>
       </c>
     </row>
   </sheetData>
